--- a/ref-data/2026-3月派工/整理後派工單.xlsx
+++ b/ref-data/2026-3月派工/整理後派工單.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H38"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -1061,9 +1061,347 @@
         <v>欽.緯.智.賢.傑.劉.叡</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>3月10日</v>
+      </c>
+      <c r="B26" t="str">
+        <v>夜班</v>
+      </c>
+      <c r="C26" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="D26" t="str">
+        <v>碩</v>
+      </c>
+      <c r="E26" t="str">
+        <v>市道102甲線(0K+000~5K+000)(新增槽化30</v>
+      </c>
+      <c r="F26" t="str">
+        <v>0.45</v>
+      </c>
+      <c r="G26" t="str">
+        <v>1383.6871</v>
+      </c>
+      <c r="H26" t="str">
+        <v>融.禮.龍.蕭.建.23</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>3月10日</v>
+      </c>
+      <c r="B27" t="str">
+        <v>夜班</v>
+      </c>
+      <c r="C27" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v>多張完成照(須標示路名巷口</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v>1383.6871</v>
+      </c>
+      <c r="H27" t="str">
+        <v>融.禮.龍.蕭.建.23</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>3月10日</v>
+      </c>
+      <c r="B28" t="str">
+        <v>夜班</v>
+      </c>
+      <c r="C28" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v>稻田</v>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v>1383.6871</v>
+      </c>
+      <c r="H28" t="str">
+        <v>融.禮.龍.蕭.建.23</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>3月10日</v>
+      </c>
+      <c r="B29" t="str">
+        <v>夜班</v>
+      </c>
+      <c r="C29" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="D29" t="str">
+        <v>碩</v>
+      </c>
+      <c r="E29" t="str">
+        <v>市道106 線 (50K+000~70K+000)</v>
+      </c>
+      <c r="F29" t="str">
+        <v>0.45</v>
+      </c>
+      <c r="G29" t="str">
+        <v>229.7771</v>
+      </c>
+      <c r="H29" t="str">
+        <v>旻.淵.劉.億.叡.21.13</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>3月10日</v>
+      </c>
+      <c r="B30" t="str">
+        <v>夜班</v>
+      </c>
+      <c r="C30" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v>多張完成照(須標示路名巷口</v>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v>229.7771</v>
+      </c>
+      <c r="H30" t="str">
+        <v>旻.淵.劉.億.叡.21.13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>3月10日</v>
+      </c>
+      <c r="B31" t="str">
+        <v>夜班</v>
+      </c>
+      <c r="C31" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="D31" t="str">
+        <v>碩</v>
+      </c>
+      <c r="E31" t="str">
+        <v>八下一派*2</v>
+      </c>
+      <c r="F31" t="str">
+        <v>採圖.錄影.噴點</v>
+      </c>
+      <c r="G31" t="str">
+        <v>5060</v>
+      </c>
+      <c r="H31" t="str">
+        <v>欽.賢.智</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>3月10日</v>
+      </c>
+      <c r="B32" t="str">
+        <v>夜班</v>
+      </c>
+      <c r="C32" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v>大園一派*15</v>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v>5060</v>
+      </c>
+      <c r="H32" t="str">
+        <v>欽.賢.智</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>3月10日</v>
+      </c>
+      <c r="B33" t="str">
+        <v>夜班</v>
+      </c>
+      <c r="C33" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v>士林區美崙街(文林路~華榮街)</v>
+      </c>
+      <c r="F33" t="str">
+        <v>預估數量</v>
+      </c>
+      <c r="G33" t="str">
+        <v>5060</v>
+      </c>
+      <c r="H33" t="str">
+        <v>欽.賢.智</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>3月10日</v>
+      </c>
+      <c r="B34" t="str">
+        <v>夜班</v>
+      </c>
+      <c r="C34" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v>美崙街(華榮街-美崙街62巷</v>
+      </c>
+      <c r="F34" t="str">
+        <v>預估數量</v>
+      </c>
+      <c r="G34" t="str">
+        <v>5060</v>
+      </c>
+      <c r="H34" t="str">
+        <v>欽.賢.智</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>3月11日</v>
+      </c>
+      <c r="B35" t="str">
+        <v>夜班</v>
+      </c>
+      <c r="C35" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="D35" t="str">
+        <v>碩</v>
+      </c>
+      <c r="E35" t="str">
+        <v>市道102甲線(0K+000~5K+000)(新增槽化30</v>
+      </c>
+      <c r="F35" t="str">
+        <v>0.45</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v>融.禮.龍.蕭.23</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>3月11日</v>
+      </c>
+      <c r="B36" t="str">
+        <v>夜班</v>
+      </c>
+      <c r="C36" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v>製組*2，多張完成照</v>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v>融.禮.龍.蕭.23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>3月11日</v>
+      </c>
+      <c r="B37" t="str">
+        <v>夜班</v>
+      </c>
+      <c r="C37" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="D37" t="str">
+        <v>碩</v>
+      </c>
+      <c r="E37" t="str">
+        <v>市道106 線 (50K+000~70K+000)</v>
+      </c>
+      <c r="F37" t="str">
+        <v>0.45</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v>欽.緯.賢.叡.旻.淵.劉.億.建13.21</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>3月11日</v>
+      </c>
+      <c r="B38" t="str">
+        <v>夜班</v>
+      </c>
+      <c r="C38" t="str">
+        <v>22:00</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v>多張完成照</v>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v>欽.緯.賢.叡.旻.淵.劉.億.建13.21</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H38"/>
   </ignoredErrors>
 </worksheet>
 </file>